--- a/schoolDocs/StudentImportData/Nursery_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Nursery_ImportReady.xlsx
@@ -95,7 +95,7 @@
     <t>general</t>
   </si>
   <si>
-    <t>04/12/2024</t>
+    <t>25/12/2024</t>
   </si>
   <si>
     <t>Chaufula</t>
@@ -110,7 +110,7 @@
     <t>rte</t>
   </si>
   <si>
-    <t>21/01/2025</t>
+    <t>03/01/2025</t>
   </si>
   <si>
     <t>Varvand</t>
@@ -131,7 +131,7 @@
     <t>Rajvir Khanderao Devkar</t>
   </si>
   <si>
-    <t>02/12/2024</t>
+    <t>10/01/2025</t>
   </si>
   <si>
     <t>Kedgaon</t>
@@ -143,46 +143,46 @@
     <t>discount</t>
   </si>
   <si>
+    <t>09/02/2025</t>
+  </si>
+  <si>
+    <t>Aaradhya Devidas Kalapahad</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>26/12/2024</t>
+  </si>
+  <si>
+    <t>Baravkarvadi</t>
+  </si>
+  <si>
+    <t>3km</t>
+  </si>
+  <si>
+    <t>Worker</t>
+  </si>
+  <si>
+    <t>Sukanya Hake</t>
+  </si>
+  <si>
     <t>29/01/2025</t>
   </si>
   <si>
-    <t>Aaradhya Devidas Kalapahad</t>
-  </si>
-  <si>
-    <t>female</t>
-  </si>
-  <si>
-    <t>20/01/2025</t>
-  </si>
-  <si>
-    <t>Baravkarvadi</t>
-  </si>
-  <si>
-    <t>3km</t>
-  </si>
-  <si>
-    <t>Worker</t>
-  </si>
-  <si>
-    <t>Sukanya Hake</t>
-  </si>
-  <si>
-    <t>26/12/2024</t>
-  </si>
-  <si>
     <t>Khutbav</t>
   </si>
   <si>
     <t>10km</t>
   </si>
   <si>
-    <t>Custom fee ₹2500 — collected ₹0 outstanding</t>
+    <t>Custom fee ₹2500</t>
   </si>
   <si>
     <t>Sanchita Gautam</t>
   </si>
   <si>
-    <t>13/01/2025</t>
+    <t>06/01/2025</t>
   </si>
   <si>
     <t>100% discount — confirm with admin</t>
@@ -583,27 +583,27 @@
   <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="31.707" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="52.844" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="31.707" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="23.423" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="52.844" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -693,8 +693,10 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2">
-        <v>5000</v>
+        <v>16200</v>
       </c>
       <c r="L2" t="s">
         <v>26</v>
@@ -728,6 +730,11 @@
       <c r="H3" t="s">
         <v>30</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3">
+        <v>0</v>
+      </c>
       <c r="L3" t="s">
         <v>31</v>
       </c>
@@ -769,6 +776,8 @@
       <c r="H4" t="s">
         <v>25</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4">
         <v>16200</v>
       </c>
@@ -807,8 +816,9 @@
       <c r="I5">
         <v>50</v>
       </c>
+      <c r="J5"/>
       <c r="K5">
-        <v>2000</v>
+        <v>8100</v>
       </c>
       <c r="L5" t="s">
         <v>42</v>
@@ -842,8 +852,8 @@
       <c r="J6">
         <v>6000</v>
       </c>
-      <c r="K6" s="5">
-        <v>6000</v>
+      <c r="K6">
+        <v>0</v>
       </c>
       <c r="L6" t="s">
         <v>45</v>
@@ -860,7 +870,6 @@
       <c r="R6" t="s">
         <v>35</v>
       </c>
-      <c r="U6" s="5"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
@@ -884,10 +893,13 @@
       <c r="H7" t="s">
         <v>41</v>
       </c>
+      <c r="I7"/>
       <c r="J7">
         <v>2500</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7">
+        <v>2500.0</v>
+      </c>
       <c r="L7" t="s">
         <v>50</v>
       </c>
@@ -922,6 +934,10 @@
       </c>
       <c r="I8">
         <v>100</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8">
+        <v>0</v>
       </c>
       <c r="L8" t="s">
         <v>55</v>

--- a/schoolDocs/StudentImportData/Nursery_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Nursery_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Kamlesh Lakshman Chaudhari</t>
@@ -125,7 +151,7 @@
     <t>Home maker</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000001</t>
   </si>
   <si>
     <t>Rajvir Khanderao Devkar</t>
@@ -176,16 +202,10 @@
     <t>10km</t>
   </si>
   <si>
-    <t>Custom fee ₹2500</t>
-  </si>
-  <si>
     <t>Sanchita Gautam</t>
   </si>
   <si>
     <t>06/01/2025</t>
-  </si>
-  <si>
-    <t>100% discount — confirm with admin</t>
   </si>
 </sst>
 </file>
@@ -237,12 +257,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -250,6 +264,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -271,16 +291,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,7 +623,7 @@
     <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="52.844" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -637,10 +657,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -667,7 +687,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -707,6 +727,7 @@
       <c r="N2" t="s">
         <v>28</v>
       </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
@@ -790,6 +811,7 @@
       <c r="N4" t="s">
         <v>33</v>
       </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
@@ -823,6 +845,7 @@
       <c r="L5" t="s">
         <v>42</v>
       </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
@@ -870,6 +893,7 @@
       <c r="R6" t="s">
         <v>35</v>
       </c>
+      <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
@@ -909,16 +933,14 @@
       <c r="N7" t="s">
         <v>52</v>
       </c>
-      <c r="U7" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="U7" s="4"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
         <v>44</v>
@@ -940,11 +962,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>55</v>
-      </c>
-      <c r="U8" t="s">
-        <v>56</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="U8"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -958,6 +978,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>